--- a/engine/techniques/breakeven_payroll/resources/templates/breakeven_payroll_input_template.xlsx
+++ b/engine/techniques/breakeven_payroll/resources/templates/breakeven_payroll_input_template.xlsx
@@ -16,9 +16,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="actuals_for_charts" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scalars" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="control_vintage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="output_breakeven_series" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="output_scenario_grid" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="output_history" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -723,192 +720,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00538135"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>OUTPUT — historical + projected breakeven (engine writes here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Written by the engine on each run. Quarterly smoothed breakeven path; each point flagged realized vs projected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>breakeven_smoothed (jobs/mo)</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>realized_or_projected</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00538135"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>OUTPUT — scenario grid (engine writes here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Written by the engine on each run. Delta-vs-Census and absolute pace/breakeven per scenario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>preset</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>migration</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>ustar_basis</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>delta_per_month (k/mo)</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>pace_kmo (k/mo)</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>breakeven_kmo (k/mo)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00538135"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>OUTPUT — run history (engine appends here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Appended each run so you can track how the estimate moves over time (the fan collapsing onto the realized path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>run_date</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>last_realized_month</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>scenario_M</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>breakeven_headline (k/mo)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12433,7 +12244,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -28954,21 +28764,21 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" t="n">
+      <c r="A791" s="25" t="n">
         <v>2025</v>
       </c>
-      <c r="B791" t="n">
+      <c r="B791" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="C791" t="n">
+      <c r="C791" s="26" t="n">
         <v>273385</v>
       </c>
-      <c r="D791" t="inlineStr">
+      <c r="D791" s="7" t="inlineStr">
         <is>
           <t>fred_cnp16ov</t>
         </is>
       </c>
-      <c r="E791" t="inlineStr">
+      <c r="E791" s="7" t="inlineStr">
         <is>
           <t>V2024</t>
         </is>
